--- a/docs/collections/gakken/metadata/data.xlsx
+++ b/docs/collections/gakken/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="4380">
   <si>
     <t>書名</t>
   </si>
@@ -12921,6 +12921,240 @@
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4ff4d3a3-675e-5bf4-6490-2be37aad8148/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 緒卷上</t>
+  </si>
+  <si>
+    <t>XA70:216</t>
+  </si>
+  <si>
+    <t>ソウモク キンヨウシュウ</t>
+  </si>
+  <si>
+    <t>水のけんちうきやう覚輯 ; 大岡雲峰, 關根雲停冩生</t>
+  </si>
+  <si>
+    <t>[東京] : 内山長太郎</t>
+  </si>
+  <si>
+    <t>明治13(1880) 序</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 3巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b622829e-378f-08ce-396b-d0a903b4221e.json</t>
+  </si>
+  <si>
+    <t>b622829e-378f-08ce-396b-d0a903b4221e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/b622829e-378f-08ce-396b-d0a903b4221e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a473717cf9ac3e5320c2e94a0e26ae331190ff2c.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155829</t>
+  </si>
+  <si>
+    <t>0465</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b622829e-378f-08ce-396b-d0a903b4221e/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 緒卷下</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 4巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ff671f97-6969-628b-5fcf-87b7d7c04600.json</t>
+  </si>
+  <si>
+    <t>ff671f97-6969-628b-5fcf-87b7d7c04600</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/ff671f97-6969-628b-5fcf-87b7d7c04600</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/213e6d9bb426daa88a7f83697fbe4a17672a8a62.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155828</t>
+  </si>
+  <si>
+    <t>0466</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ff671f97-6969-628b-5fcf-87b7d7c04600/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 1之卷</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 5巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8f7a3d8e-7535-a0c8-4598-e8527dcd5c5d.json</t>
+  </si>
+  <si>
+    <t>8f7a3d8e-7535-a0c8-4598-e8527dcd5c5d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/8f7a3d8e-7535-a0c8-4598-e8527dcd5c5d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/778ef93693b35d563d4202a8494b516eeffc9200.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155827</t>
+  </si>
+  <si>
+    <t>0467</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8f7a3d8e-7535-a0c8-4598-e8527dcd5c5d/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 2之卷</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 6巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f2713537-62bf-4f32-8500-ebde332ba499.json</t>
+  </si>
+  <si>
+    <t>f2713537-62bf-4f32-8500-ebde332ba499</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/f2713537-62bf-4f32-8500-ebde332ba499</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/02b63bbe88aaa591a97d4f9bd049dbc4f72c93ba.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155826</t>
+  </si>
+  <si>
+    <t>0468</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f2713537-62bf-4f32-8500-ebde332ba499/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 3之卷</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 7巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c51897c6-2ca2-a712-8026-001c86119e3d.json</t>
+  </si>
+  <si>
+    <t>c51897c6-2ca2-a712-8026-001c86119e3d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/c51897c6-2ca2-a712-8026-001c86119e3d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14656fad9b23646faf2d109ef705d61d3614b8e9.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155825</t>
+  </si>
+  <si>
+    <t>0469</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c51897c6-2ca2-a712-8026-001c86119e3d/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 4之卷</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 8巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e77264e8-30fd-6da0-711e-6def80752e85.json</t>
+  </si>
+  <si>
+    <t>e77264e8-30fd-6da0-711e-6def80752e85</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/e77264e8-30fd-6da0-711e-6def80752e85</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6db01f898326f008fbb50772d0e649e8587b6098.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155824</t>
+  </si>
+  <si>
+    <t>0470</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e77264e8-30fd-6da0-711e-6def80752e85/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 5之卷</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 9巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/36f17ad6-640d-440a-5e29-dc41a8850483.json</t>
+  </si>
+  <si>
+    <t>36f17ad6-640d-440a-5e29-dc41a8850483</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/36f17ad6-640d-440a-5e29-dc41a8850483</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ef8bc6682166b9565a0911815575d5cd8250772d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155823</t>
+  </si>
+  <si>
+    <t>0471</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/36f17ad6-640d-440a-5e29-dc41a8850483/manifest</t>
+  </si>
+  <si>
+    <t>草木錦葉集 6之卷</t>
+  </si>
+  <si>
+    <t>緒卷の巻尾及び1-6の巻の見出の書名: 錦葉集|見返しの書名: 草木きむ葉しふ|文政12年出板の後印|刊記に「文政十二己丑年十月」「東京栽花園藏版」とあり|見返しに「東都 花園 栽花園蔵板 書肆 千鍾房發行」とあり|又丁あり|1-3之卷: 前編. 4-6之卷: 後編|印記: 「小栗嘉兵エ」,「祢宜主人」,「阿部米吉」|錦葉集, ,草木きむ葉しふ, 草木喜舞葉志布|26cm|【内容注記】:前編草木錦葉集 3巻 / 水のげんちうきやう覚輯|【内容注記】:後編草木錦葉集 10巻 / 水のちうきやう覺輯</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/68740f57-0095-8b15-5197-bb579a925f74.json</t>
+  </si>
+  <si>
+    <t>68740f57-0095-8b15-5197-bb579a925f74</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/gakken/document/68740f57-0095-8b15-5197-bb579a925f74</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2469ac83a69fa7d65ac0b3e4a5bb3d368b624926.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1155822</t>
+  </si>
+  <si>
+    <t>0472</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/68740f57-0095-8b15-5197-bb579a925f74/manifest</t>
   </si>
 </sst>
 </file>
@@ -13256,7 +13490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC466"/>
+  <dimension ref="A1:AC474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -13434,7 +13668,7 @@
         <v>55</v>
       </c>
       <c r="AC2" t="n">
-        <v>30454</v>
+        <v>30753</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -49131,6 +49365,622 @@
         <v>43</v>
       </c>
     </row>
+    <row r="467" spans="1:29">
+      <c r="A467" t="s">
+        <v>4302</v>
+      </c>
+      <c r="B467" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C467" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D467" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E467" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F467" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G467" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H467" t="s">
+        <v>62</v>
+      </c>
+      <c r="I467" t="s">
+        <v>82</v>
+      </c>
+      <c r="J467" t="s">
+        <v>4308</v>
+      </c>
+      <c r="K467" t="s">
+        <v>4309</v>
+      </c>
+      <c r="L467" t="s">
+        <v>4310</v>
+      </c>
+      <c r="M467" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N467" t="s">
+        <v>4312</v>
+      </c>
+      <c r="O467" t="s">
+        <v>69</v>
+      </c>
+      <c r="P467" t="s">
+        <v>4313</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>4314</v>
+      </c>
+      <c r="R467" t="s">
+        <v>72</v>
+      </c>
+      <c r="S467" t="s">
+        <v>73</v>
+      </c>
+      <c r="T467" t="s"/>
+      <c r="U467" t="s">
+        <v>74</v>
+      </c>
+      <c r="V467" t="s">
+        <v>4315</v>
+      </c>
+      <c r="W467" t="s"/>
+      <c r="X467" t="s">
+        <v>4316</v>
+      </c>
+      <c r="Y467" t="s"/>
+      <c r="Z467" t="s"/>
+      <c r="AA467" t="s"/>
+      <c r="AB467" t="s"/>
+      <c r="AC467" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="468" spans="1:29">
+      <c r="A468" t="s">
+        <v>4317</v>
+      </c>
+      <c r="B468" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C468" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D468" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E468" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F468" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G468" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H468" t="s">
+        <v>62</v>
+      </c>
+      <c r="I468" t="s">
+        <v>82</v>
+      </c>
+      <c r="J468" t="s">
+        <v>4318</v>
+      </c>
+      <c r="K468" t="s">
+        <v>4319</v>
+      </c>
+      <c r="L468" t="s">
+        <v>4320</v>
+      </c>
+      <c r="M468" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N468" t="s">
+        <v>4321</v>
+      </c>
+      <c r="O468" t="s">
+        <v>69</v>
+      </c>
+      <c r="P468" t="s">
+        <v>4322</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>4323</v>
+      </c>
+      <c r="R468" t="s">
+        <v>72</v>
+      </c>
+      <c r="S468" t="s">
+        <v>73</v>
+      </c>
+      <c r="T468" t="s"/>
+      <c r="U468" t="s">
+        <v>74</v>
+      </c>
+      <c r="V468" t="s">
+        <v>4324</v>
+      </c>
+      <c r="W468" t="s"/>
+      <c r="X468" t="s">
+        <v>4325</v>
+      </c>
+      <c r="Y468" t="s"/>
+      <c r="Z468" t="s"/>
+      <c r="AA468" t="s"/>
+      <c r="AB468" t="s"/>
+      <c r="AC468" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="469" spans="1:29">
+      <c r="A469" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B469" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C469" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D469" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E469" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F469" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G469" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H469" t="s">
+        <v>62</v>
+      </c>
+      <c r="I469" t="s">
+        <v>82</v>
+      </c>
+      <c r="J469" t="s">
+        <v>4327</v>
+      </c>
+      <c r="K469" t="s">
+        <v>4328</v>
+      </c>
+      <c r="L469" t="s">
+        <v>4329</v>
+      </c>
+      <c r="M469" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N469" t="s">
+        <v>4330</v>
+      </c>
+      <c r="O469" t="s">
+        <v>69</v>
+      </c>
+      <c r="P469" t="s">
+        <v>4331</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>4332</v>
+      </c>
+      <c r="R469" t="s">
+        <v>72</v>
+      </c>
+      <c r="S469" t="s">
+        <v>73</v>
+      </c>
+      <c r="T469" t="s"/>
+      <c r="U469" t="s">
+        <v>74</v>
+      </c>
+      <c r="V469" t="s">
+        <v>4333</v>
+      </c>
+      <c r="W469" t="s"/>
+      <c r="X469" t="s">
+        <v>4334</v>
+      </c>
+      <c r="Y469" t="s"/>
+      <c r="Z469" t="s"/>
+      <c r="AA469" t="s"/>
+      <c r="AB469" t="s"/>
+      <c r="AC469" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="470" spans="1:29">
+      <c r="A470" t="s">
+        <v>4335</v>
+      </c>
+      <c r="B470" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C470" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D470" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E470" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F470" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G470" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H470" t="s">
+        <v>62</v>
+      </c>
+      <c r="I470" t="s">
+        <v>82</v>
+      </c>
+      <c r="J470" t="s">
+        <v>4336</v>
+      </c>
+      <c r="K470" t="s">
+        <v>4337</v>
+      </c>
+      <c r="L470" t="s">
+        <v>4338</v>
+      </c>
+      <c r="M470" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N470" t="s">
+        <v>4339</v>
+      </c>
+      <c r="O470" t="s">
+        <v>69</v>
+      </c>
+      <c r="P470" t="s">
+        <v>4340</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>4341</v>
+      </c>
+      <c r="R470" t="s">
+        <v>72</v>
+      </c>
+      <c r="S470" t="s">
+        <v>73</v>
+      </c>
+      <c r="T470" t="s"/>
+      <c r="U470" t="s">
+        <v>74</v>
+      </c>
+      <c r="V470" t="s">
+        <v>4342</v>
+      </c>
+      <c r="W470" t="s"/>
+      <c r="X470" t="s">
+        <v>4343</v>
+      </c>
+      <c r="Y470" t="s"/>
+      <c r="Z470" t="s"/>
+      <c r="AA470" t="s"/>
+      <c r="AB470" t="s"/>
+      <c r="AC470" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="471" spans="1:29">
+      <c r="A471" t="s">
+        <v>4344</v>
+      </c>
+      <c r="B471" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C471" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D471" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E471" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F471" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G471" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H471" t="s">
+        <v>62</v>
+      </c>
+      <c r="I471" t="s">
+        <v>82</v>
+      </c>
+      <c r="J471" t="s">
+        <v>4345</v>
+      </c>
+      <c r="K471" t="s">
+        <v>4346</v>
+      </c>
+      <c r="L471" t="s">
+        <v>4347</v>
+      </c>
+      <c r="M471" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N471" t="s">
+        <v>4348</v>
+      </c>
+      <c r="O471" t="s">
+        <v>69</v>
+      </c>
+      <c r="P471" t="s">
+        <v>4349</v>
+      </c>
+      <c r="Q471" t="s">
+        <v>4350</v>
+      </c>
+      <c r="R471" t="s">
+        <v>72</v>
+      </c>
+      <c r="S471" t="s">
+        <v>73</v>
+      </c>
+      <c r="T471" t="s"/>
+      <c r="U471" t="s">
+        <v>74</v>
+      </c>
+      <c r="V471" t="s">
+        <v>4351</v>
+      </c>
+      <c r="W471" t="s"/>
+      <c r="X471" t="s">
+        <v>4352</v>
+      </c>
+      <c r="Y471" t="s"/>
+      <c r="Z471" t="s"/>
+      <c r="AA471" t="s"/>
+      <c r="AB471" t="s"/>
+      <c r="AC471" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="472" spans="1:29">
+      <c r="A472" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B472" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C472" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D472" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E472" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F472" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G472" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H472" t="s">
+        <v>62</v>
+      </c>
+      <c r="I472" t="s">
+        <v>82</v>
+      </c>
+      <c r="J472" t="s">
+        <v>4354</v>
+      </c>
+      <c r="K472" t="s">
+        <v>4355</v>
+      </c>
+      <c r="L472" t="s">
+        <v>4356</v>
+      </c>
+      <c r="M472" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N472" t="s">
+        <v>4357</v>
+      </c>
+      <c r="O472" t="s">
+        <v>69</v>
+      </c>
+      <c r="P472" t="s">
+        <v>4358</v>
+      </c>
+      <c r="Q472" t="s">
+        <v>4359</v>
+      </c>
+      <c r="R472" t="s">
+        <v>72</v>
+      </c>
+      <c r="S472" t="s">
+        <v>73</v>
+      </c>
+      <c r="T472" t="s"/>
+      <c r="U472" t="s">
+        <v>74</v>
+      </c>
+      <c r="V472" t="s">
+        <v>4360</v>
+      </c>
+      <c r="W472" t="s"/>
+      <c r="X472" t="s">
+        <v>4361</v>
+      </c>
+      <c r="Y472" t="s"/>
+      <c r="Z472" t="s"/>
+      <c r="AA472" t="s"/>
+      <c r="AB472" t="s"/>
+      <c r="AC472" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="473" spans="1:29">
+      <c r="A473" t="s">
+        <v>4362</v>
+      </c>
+      <c r="B473" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C473" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D473" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E473" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F473" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G473" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H473" t="s">
+        <v>62</v>
+      </c>
+      <c r="I473" t="s">
+        <v>82</v>
+      </c>
+      <c r="J473" t="s">
+        <v>4363</v>
+      </c>
+      <c r="K473" t="s">
+        <v>4364</v>
+      </c>
+      <c r="L473" t="s">
+        <v>4365</v>
+      </c>
+      <c r="M473" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N473" t="s">
+        <v>4366</v>
+      </c>
+      <c r="O473" t="s">
+        <v>69</v>
+      </c>
+      <c r="P473" t="s">
+        <v>4367</v>
+      </c>
+      <c r="Q473" t="s">
+        <v>4368</v>
+      </c>
+      <c r="R473" t="s">
+        <v>72</v>
+      </c>
+      <c r="S473" t="s">
+        <v>73</v>
+      </c>
+      <c r="T473" t="s"/>
+      <c r="U473" t="s">
+        <v>74</v>
+      </c>
+      <c r="V473" t="s">
+        <v>4369</v>
+      </c>
+      <c r="W473" t="s"/>
+      <c r="X473" t="s">
+        <v>4370</v>
+      </c>
+      <c r="Y473" t="s"/>
+      <c r="Z473" t="s"/>
+      <c r="AA473" t="s"/>
+      <c r="AB473" t="s"/>
+      <c r="AC473" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="474" spans="1:29">
+      <c r="A474" t="s">
+        <v>4371</v>
+      </c>
+      <c r="B474" t="s">
+        <v>4303</v>
+      </c>
+      <c r="C474" t="s">
+        <v>4304</v>
+      </c>
+      <c r="D474" t="s">
+        <v>4305</v>
+      </c>
+      <c r="E474" t="s">
+        <v>3139</v>
+      </c>
+      <c r="F474" t="s">
+        <v>4306</v>
+      </c>
+      <c r="G474" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H474" t="s">
+        <v>62</v>
+      </c>
+      <c r="I474" t="s">
+        <v>82</v>
+      </c>
+      <c r="J474" t="s">
+        <v>4372</v>
+      </c>
+      <c r="K474" t="s">
+        <v>4373</v>
+      </c>
+      <c r="L474" t="s">
+        <v>4374</v>
+      </c>
+      <c r="M474" t="s">
+        <v>4311</v>
+      </c>
+      <c r="N474" t="s">
+        <v>4375</v>
+      </c>
+      <c r="O474" t="s">
+        <v>69</v>
+      </c>
+      <c r="P474" t="s">
+        <v>4376</v>
+      </c>
+      <c r="Q474" t="s">
+        <v>4377</v>
+      </c>
+      <c r="R474" t="s">
+        <v>72</v>
+      </c>
+      <c r="S474" t="s">
+        <v>73</v>
+      </c>
+      <c r="T474" t="s"/>
+      <c r="U474" t="s">
+        <v>74</v>
+      </c>
+      <c r="V474" t="s">
+        <v>4378</v>
+      </c>
+      <c r="W474" t="s"/>
+      <c r="X474" t="s">
+        <v>4379</v>
+      </c>
+      <c r="Y474" t="s"/>
+      <c r="Z474" t="s"/>
+      <c r="AA474" t="s"/>
+      <c r="AB474" t="s"/>
+      <c r="AC474" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
